--- a/research/traditional_assets/database/data/romania/romania_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.19945</v>
+        <v>0.138</v>
       </c>
       <c r="E2">
-        <v>0.112</v>
+        <v>0.19</v>
       </c>
       <c r="G2">
-        <v>0.04405594405594405</v>
+        <v>0.1064595993697952</v>
       </c>
       <c r="H2">
-        <v>0.04405594405594405</v>
+        <v>0.1064595993697952</v>
       </c>
       <c r="I2">
-        <v>0.9086538461538461</v>
+        <v>0.8977342636356814</v>
       </c>
       <c r="J2">
-        <v>0.8668030690671784</v>
+        <v>0.8603639133853898</v>
       </c>
       <c r="K2">
-        <v>1034</v>
+        <v>1166.8</v>
       </c>
       <c r="L2">
-        <v>0.9038461538461539</v>
+        <v>0.8753844999624877</v>
       </c>
       <c r="M2">
-        <v>350.811</v>
+        <v>313.473</v>
       </c>
       <c r="N2">
-        <v>0.09295468998410174</v>
+        <v>0.08917389696469719</v>
       </c>
       <c r="O2">
-        <v>0.3392756286266924</v>
+        <v>0.2686604388069935</v>
       </c>
       <c r="P2">
-        <v>209.46</v>
+        <v>78.706</v>
       </c>
       <c r="Q2">
-        <v>0.05550079491255961</v>
+        <v>0.022389554234347</v>
       </c>
       <c r="R2">
-        <v>0.2025725338491296</v>
+        <v>0.06745457661981488</v>
       </c>
       <c r="S2">
-        <v>141.351</v>
+        <v>234.767</v>
       </c>
       <c r="T2">
-        <v>0.4029263620582023</v>
+        <v>0.7489225547335814</v>
       </c>
       <c r="U2">
-        <v>269.23</v>
+        <v>125.17</v>
       </c>
       <c r="V2">
-        <v>0.07133810280869105</v>
+        <v>0.0356072027991921</v>
       </c>
       <c r="W2">
-        <v>0.09775888717156105</v>
+        <v>0.06008178672538535</v>
       </c>
       <c r="X2">
-        <v>0.05988483786134588</v>
+        <v>0.09434184640869402</v>
       </c>
       <c r="Y2">
-        <v>0.03787404931021517</v>
+        <v>-0.03426005968330867</v>
       </c>
       <c r="Z2">
-        <v>0.3031356521444198</v>
+        <v>0.2810967941805857</v>
       </c>
       <c r="AA2">
-        <v>0.1033074724377297</v>
+        <v>0.05629511888204518</v>
       </c>
       <c r="AB2">
-        <v>0.05965486776061259</v>
+        <v>0.09413513067646434</v>
       </c>
       <c r="AC2">
-        <v>0.04306393543848153</v>
+        <v>-0.03784001179441916</v>
       </c>
       <c r="AD2">
-        <v>15.453</v>
+        <v>10.371</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>15.453</v>
+        <v>10.371</v>
       </c>
       <c r="AG2">
-        <v>-253.777</v>
+        <v>-114.799</v>
       </c>
       <c r="AH2">
-        <v>0.004077897258522536</v>
+        <v>0.002941567718598814</v>
       </c>
       <c r="AI2">
-        <v>0.003068230756844152</v>
+        <v>0.002113868432225456</v>
       </c>
       <c r="AJ2">
-        <v>-0.07209117149680574</v>
+        <v>-0.03375943721234018</v>
       </c>
       <c r="AK2">
-        <v>-0.05323371698785646</v>
+        <v>-0.02401149884720794</v>
       </c>
       <c r="AL2">
-        <v>0.5820000000000001</v>
+        <v>0.397</v>
       </c>
       <c r="AM2">
-        <v>0.5820000000000001</v>
+        <v>0.397</v>
       </c>
       <c r="AN2">
-        <v>0.09031560490940971</v>
+        <v>0.109630021141649</v>
       </c>
       <c r="AO2">
-        <v>1786.082474226804</v>
+        <v>3014.080604534005</v>
       </c>
       <c r="AP2">
-        <v>-1.483208649912332</v>
+        <v>-1.213520084566596</v>
       </c>
       <c r="AQ2">
-        <v>1786.082474226804</v>
+        <v>3014.080604534005</v>
       </c>
     </row>
     <row r="3">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.469</v>
+        <v>0.418</v>
       </c>
       <c r="E3">
-        <v>0.534</v>
+        <v>0.473</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -734,67 +734,67 @@
         <v>0</v>
       </c>
       <c r="I3">
-        <v>0.9759642258244829</v>
+        <v>0.9787704555506413</v>
       </c>
       <c r="J3">
-        <v>0.9743540190357716</v>
+        <v>0.9775691752146796</v>
       </c>
       <c r="K3">
-        <v>871.3</v>
+        <v>1074.2</v>
       </c>
       <c r="L3">
-        <v>0.9740637227501396</v>
+        <v>0.9501990269792128</v>
       </c>
       <c r="M3">
-        <v>305</v>
+        <v>278.7</v>
       </c>
       <c r="N3">
-        <v>0.1075041415529943</v>
+        <v>0.1046957175056349</v>
       </c>
       <c r="O3">
-        <v>0.3500516469643062</v>
+        <v>0.2594488921988456</v>
       </c>
       <c r="P3">
-        <v>180.6</v>
+        <v>59.3</v>
       </c>
       <c r="Q3">
-        <v>0.06365655070318282</v>
+        <v>0.02227648384673178</v>
       </c>
       <c r="R3">
-        <v>0.2072764834155859</v>
+        <v>0.05520387264941351</v>
       </c>
       <c r="S3">
-        <v>124.4</v>
+        <v>219.4</v>
       </c>
       <c r="T3">
-        <v>0.4078688524590164</v>
+        <v>0.7872264083243631</v>
       </c>
       <c r="U3">
-        <v>104.4</v>
+        <v>55.3</v>
       </c>
       <c r="V3">
-        <v>0.03679813894469705</v>
+        <v>0.02077385424492862</v>
       </c>
       <c r="W3">
-        <v>0.3649118398458768</v>
+        <v>0.3740641431904447</v>
       </c>
       <c r="X3">
-        <v>0.0595317852970933</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="Y3">
-        <v>0.3053800545487835</v>
+        <v>0.2800238004682528</v>
       </c>
       <c r="Z3">
-        <v>0.4146386687062533</v>
+        <v>0.4085209409894121</v>
       </c>
       <c r="AA3">
-        <v>0.4040048533015797</v>
+        <v>0.3993574793409444</v>
       </c>
       <c r="AB3">
-        <v>0.0595317852970933</v>
+        <v>0.09404034272219189</v>
       </c>
       <c r="AC3">
-        <v>0.3444730680044864</v>
+        <v>0.3053171366187525</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -806,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-104.4</v>
+        <v>-55.3</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -815,22 +815,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-0.0382039740915578</v>
+        <v>-0.02121456247362566</v>
       </c>
       <c r="AK3">
-        <v>-0.03772630361724425</v>
+        <v>-0.01843026162306282</v>
       </c>
       <c r="AL3">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="AM3">
-        <v>0.021</v>
+        <v>0.012</v>
       </c>
       <c r="AO3">
-        <v>41571.42857142857</v>
+        <v>92208.33333333333</v>
       </c>
       <c r="AQ3">
-        <v>41571.42857142857</v>
+        <v>92208.33333333333</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIF Banat-Crisana (BVB:SIF1)</t>
+          <t>S.I.F. Oltenia S.A. (BVB:SIF5)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,115 +850,109 @@
         </is>
       </c>
       <c r="G4">
-        <v>0.1788413098236776</v>
+        <v>0.0974188176519567</v>
       </c>
       <c r="H4">
-        <v>0.1788413098236776</v>
+        <v>0.0974188176519567</v>
       </c>
       <c r="I4">
-        <v>0.9109991603694375</v>
+        <v>0.3430474604496254</v>
       </c>
       <c r="J4">
-        <v>0.8784516449126022</v>
+        <v>0.3179013585478144</v>
       </c>
       <c r="K4">
-        <v>106</v>
+        <v>38.6</v>
       </c>
       <c r="L4">
-        <v>0.8900083963056256</v>
+        <v>0.3213988343047461</v>
       </c>
       <c r="M4">
-        <v>0.001</v>
+        <v>5.781999999999999</v>
       </c>
       <c r="N4">
-        <v>3.33889816360601e-06</v>
+        <v>0.03275920679886685</v>
       </c>
       <c r="O4">
-        <v>9.433962264150944e-06</v>
+        <v>0.1497927461139896</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>5.77</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.03269121813031161</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.1494818652849741</v>
       </c>
       <c r="S4">
-        <v>0.001</v>
+        <v>0.01199999999999957</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.00207540643375987</v>
       </c>
       <c r="U4">
-        <v>76.09999999999999</v>
+        <v>2.78</v>
       </c>
       <c r="V4">
-        <v>0.2540901502504174</v>
+        <v>0.01575070821529745</v>
       </c>
       <c r="W4">
-        <v>0.1773168283706925</v>
+        <v>0.07746337547662051</v>
       </c>
       <c r="X4">
-        <v>0.05955459015197099</v>
+        <v>0.09562300201441615</v>
       </c>
       <c r="Y4">
-        <v>0.1177622382187216</v>
+        <v>-0.01815962653779564</v>
       </c>
       <c r="Z4">
-        <v>0.2189990401553404</v>
+        <v>0.247695258522903</v>
       </c>
       <c r="AA4">
-        <v>0.1923800670587398</v>
+        <v>0.07874265919028298</v>
       </c>
       <c r="AB4">
-        <v>0.0595398059130897</v>
+        <v>0.09452462098381804</v>
       </c>
       <c r="AC4">
-        <v>0.1328402611456501</v>
+        <v>-0.01578196179353507</v>
       </c>
       <c r="AD4">
-        <v>0.183</v>
+        <v>6.02</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.183</v>
+        <v>6.02</v>
       </c>
       <c r="AG4">
-        <v>-75.91699999999999</v>
+        <v>3.24</v>
       </c>
       <c r="AH4">
-        <v>0.0006106452484792264</v>
+        <v>0.03298268682884067</v>
       </c>
       <c r="AI4">
-        <v>0.0002324154826812364</v>
+        <v>0.01170022545284926</v>
       </c>
       <c r="AJ4">
-        <v>-0.339547282217342</v>
+        <v>0.01802603760988094</v>
       </c>
       <c r="AK4">
-        <v>-0.1067324820078646</v>
+        <v>0.006331340133661625</v>
       </c>
       <c r="AL4">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AM4">
-        <v>0.097</v>
+        <v>0</v>
       </c>
       <c r="AN4">
-        <v>0.001683532658693652</v>
-      </c>
-      <c r="AO4">
-        <v>1118.556701030928</v>
+        <v>0.1346756152125279</v>
       </c>
       <c r="AP4">
-        <v>-0.6984084636614534</v>
-      </c>
-      <c r="AQ4">
-        <v>1118.556701030928</v>
+        <v>0.07248322147651005</v>
       </c>
     </row>
     <row r="5">
@@ -969,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>S.I.F. Transilvania S.A. (BVB:SIF3)</t>
+          <t>Transilvania Investments Alliance S.A. (BVB:TRANSI)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -977,119 +971,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D5">
+        <v>0.138</v>
+      </c>
       <c r="E5">
-        <v>0.112</v>
+        <v>0.19</v>
       </c>
       <c r="G5">
-        <v>0.2946996466431095</v>
+        <v>0.9454545454545454</v>
       </c>
       <c r="H5">
-        <v>0.2946996466431095</v>
+        <v>0.9454545454545454</v>
       </c>
       <c r="I5">
-        <v>0.8939929328621908</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="J5">
-        <v>0.8939929328621908</v>
+        <v>0.7727272727272727</v>
       </c>
       <c r="K5">
-        <v>25.3</v>
+        <v>19.1</v>
       </c>
       <c r="L5">
-        <v>0.8939929328621908</v>
+        <v>0.8681818181818183</v>
       </c>
       <c r="M5">
-        <v>12</v>
+        <v>1.111</v>
       </c>
       <c r="N5">
-        <v>0.070298769771529</v>
+        <v>0.008666146645865836</v>
       </c>
       <c r="O5">
-        <v>0.4743083003952569</v>
+        <v>0.0581675392670157</v>
       </c>
       <c r="P5">
-        <v>12</v>
+        <v>0.216</v>
       </c>
       <c r="Q5">
-        <v>0.070298769771529</v>
+        <v>0.001684867394695788</v>
       </c>
       <c r="R5">
-        <v>0.4743083003952569</v>
+        <v>0.01130890052356021</v>
       </c>
       <c r="S5">
-        <v>0</v>
+        <v>0.895</v>
       </c>
       <c r="T5">
-        <v>0</v>
+        <v>0.8055805580558056</v>
       </c>
       <c r="U5">
-        <v>25.7</v>
+        <v>6.49</v>
       </c>
       <c r="V5">
-        <v>0.1505565319273579</v>
+        <v>0.05062402496099844</v>
       </c>
       <c r="W5">
-        <v>0.09775888717156105</v>
+        <v>0.06008178672538535</v>
       </c>
       <c r="X5">
-        <v>0.06167013329107503</v>
+        <v>0.09434184640869402</v>
       </c>
       <c r="Y5">
-        <v>0.03608875388048602</v>
+        <v>-0.03426005968330867</v>
       </c>
       <c r="Z5">
-        <v>0.115557370355247</v>
+        <v>0.07285250678852905</v>
       </c>
       <c r="AA5">
-        <v>0.1033074724377297</v>
+        <v>0.05629511888204518</v>
       </c>
       <c r="AB5">
-        <v>0.06024353699924816</v>
+        <v>0.09413513067646434</v>
       </c>
       <c r="AC5">
-        <v>0.04306393543848153</v>
+        <v>-0.03784001179441916</v>
       </c>
       <c r="AD5">
-        <v>9.779999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>9.779999999999999</v>
+        <v>0.833</v>
       </c>
       <c r="AG5">
-        <v>-15.92</v>
+        <v>-5.657</v>
       </c>
       <c r="AH5">
-        <v>0.05418882978723404</v>
+        <v>0.006455712879650942</v>
       </c>
       <c r="AI5">
-        <v>0.02984619140625</v>
+        <v>0.003273946382741233</v>
       </c>
       <c r="AJ5">
-        <v>-0.1028556661067321</v>
+        <v>-0.04616338754559624</v>
       </c>
       <c r="AK5">
-        <v>-0.05271872309424466</v>
+        <v>-0.02281572780840758</v>
       </c>
       <c r="AL5">
-        <v>0.265</v>
+        <v>0.171</v>
       </c>
       <c r="AM5">
-        <v>0.265</v>
+        <v>0.171</v>
       </c>
       <c r="AN5">
-        <v>0.3835294117647058</v>
+        <v>0.04871345029239765</v>
       </c>
       <c r="AO5">
-        <v>95.47169811320755</v>
+        <v>99.41520467836257</v>
       </c>
       <c r="AP5">
-        <v>-0.624313725490196</v>
+        <v>-0.3308187134502923</v>
       </c>
       <c r="AQ5">
-        <v>95.47169811320755</v>
+        <v>99.41520467836257</v>
       </c>
     </row>
     <row r="6">
@@ -1100,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Evergent Investments S.A. (BVB:EVER)</t>
+          <t>SIF Banat-Crisana (BVB:SIF1)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1108,122 +1105,116 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D6">
-        <v>-0.0701</v>
-      </c>
-      <c r="E6">
-        <v>-0.128</v>
-      </c>
       <c r="G6">
-        <v>0.08549618320610687</v>
+        <v>3.301003344481606</v>
       </c>
       <c r="H6">
-        <v>0.08549618320610687</v>
+        <v>3.301003344481606</v>
       </c>
       <c r="I6">
-        <v>0.5241730279898219</v>
+        <v>0.7357859531772576</v>
       </c>
       <c r="J6">
-        <v>0.4565377985717804</v>
+        <v>0.6695652173913045</v>
       </c>
       <c r="K6">
-        <v>18.9</v>
+        <v>20</v>
       </c>
       <c r="L6">
-        <v>0.4809160305343512</v>
+        <v>0.6688963210702341</v>
       </c>
       <c r="M6">
-        <v>13.98</v>
+        <v>8.559999999999999</v>
       </c>
       <c r="N6">
-        <v>0.05105916727538349</v>
+        <v>0.03213213213213213</v>
       </c>
       <c r="O6">
-        <v>0.7396825396825397</v>
+        <v>0.4279999999999999</v>
       </c>
       <c r="P6">
-        <v>7.83</v>
+        <v>3.79</v>
       </c>
       <c r="Q6">
-        <v>0.02859751643535427</v>
+        <v>0.01422672672672673</v>
       </c>
       <c r="R6">
-        <v>0.4142857142857143</v>
+        <v>0.1895</v>
       </c>
       <c r="S6">
-        <v>6.15</v>
+        <v>4.769999999999999</v>
       </c>
       <c r="T6">
-        <v>0.4399141630901288</v>
+        <v>0.5572429906542056</v>
       </c>
       <c r="U6">
-        <v>58.2</v>
+        <v>39.8</v>
       </c>
       <c r="V6">
-        <v>0.212563915266618</v>
+        <v>0.1493993993993994</v>
       </c>
       <c r="W6">
-        <v>0.04373987502892848</v>
+        <v>0.02540650406504065</v>
       </c>
       <c r="X6">
-        <v>0.05988483786134588</v>
+        <v>0.09406089611097052</v>
       </c>
       <c r="Y6">
-        <v>-0.0161449628324174</v>
+        <v>-0.06865439204592987</v>
       </c>
       <c r="Z6">
-        <v>0.09086705202312137</v>
+        <v>0.04203671393805278</v>
       </c>
       <c r="AA6">
-        <v>0.04148424389334328</v>
+        <v>0.02814632150634839</v>
       </c>
       <c r="AB6">
-        <v>0.05965486776061259</v>
+        <v>0.09404684348627286</v>
       </c>
       <c r="AC6">
-        <v>-0.01817062386726931</v>
+        <v>-0.06590052197992448</v>
       </c>
       <c r="AD6">
-        <v>2.59</v>
+        <v>0.118</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>2.59</v>
+        <v>0.118</v>
       </c>
       <c r="AG6">
-        <v>-55.61</v>
+        <v>-39.682</v>
       </c>
       <c r="AH6">
-        <v>0.009370816599732263</v>
+        <v>0.0004427468313584824</v>
       </c>
       <c r="AI6">
-        <v>0.004801720462003374</v>
+        <v>0.0001988815441297921</v>
       </c>
       <c r="AJ6">
-        <v>-0.2548696090563271</v>
+        <v>-0.1750280083628119</v>
       </c>
       <c r="AK6">
-        <v>-0.1155676551881793</v>
+        <v>-0.0716905321958816</v>
       </c>
       <c r="AL6">
-        <v>0.131</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AM6">
-        <v>0.131</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="AN6">
-        <v>0.1210280373831776</v>
+        <v>0.005339366515837104</v>
       </c>
       <c r="AO6">
-        <v>157.2519083969466</v>
+        <v>252.8735632183908</v>
       </c>
       <c r="AP6">
-        <v>-2.598598130841121</v>
+        <v>-1.795565610859728</v>
       </c>
       <c r="AQ6">
-        <v>157.2519083969466</v>
+        <v>252.8735632183908</v>
       </c>
     </row>
     <row r="7">
@@ -1234,7 +1225,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SIF Oltenia (BVB:SIF5)</t>
+          <t>Evergent Investments S.A. (BVB:EVER)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1242,116 +1233,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D7">
+        <v>-0.07290000000000001</v>
+      </c>
+      <c r="E7">
+        <v>-0.0499</v>
+      </c>
       <c r="G7">
-        <v>0.2770700636942675</v>
+        <v>0.3519736842105263</v>
       </c>
       <c r="H7">
-        <v>0.2770700636942675</v>
+        <v>0.3519736842105263</v>
       </c>
       <c r="I7">
-        <v>0.1926751592356688</v>
+        <v>0.3253289473684211</v>
       </c>
       <c r="J7">
-        <v>0.1803669550337485</v>
+        <v>0.3111421344103931</v>
       </c>
       <c r="K7">
-        <v>12.5</v>
+        <v>14.9</v>
       </c>
       <c r="L7">
-        <v>0.1990445859872612</v>
+        <v>0.4901315789473685</v>
       </c>
       <c r="M7">
-        <v>19.83</v>
+        <v>19.32</v>
       </c>
       <c r="N7">
-        <v>0.1027993779160186</v>
+        <v>0.06846208362863218</v>
       </c>
       <c r="O7">
-        <v>1.5864</v>
+        <v>1.296644295302013</v>
       </c>
       <c r="P7">
-        <v>9.029999999999999</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="Q7">
-        <v>0.04681181959564541</v>
+        <v>0.03412473423104182</v>
       </c>
       <c r="R7">
-        <v>0.7223999999999999</v>
+        <v>0.6463087248322148</v>
       </c>
       <c r="S7">
-        <v>10.8</v>
+        <v>9.69</v>
       </c>
       <c r="T7">
-        <v>0.5446293494704992</v>
+        <v>0.5015527950310559</v>
       </c>
       <c r="U7">
-        <v>4.83</v>
+        <v>20.8</v>
       </c>
       <c r="V7">
-        <v>0.02503888024883359</v>
+        <v>0.07370659107016302</v>
       </c>
       <c r="W7">
-        <v>0.03147821707378494</v>
+        <v>0.02795497185741088</v>
       </c>
       <c r="X7">
-        <v>0.06009288342557292</v>
+        <v>0.09459940161239239</v>
       </c>
       <c r="Y7">
-        <v>-0.02861466635178798</v>
+        <v>-0.0666444297549815</v>
       </c>
       <c r="Z7">
-        <v>0.1588465916276717</v>
+        <v>0.06381862076204471</v>
       </c>
       <c r="AA7">
-        <v>0.02865067604937246</v>
+        <v>0.01985666187903002</v>
       </c>
       <c r="AB7">
-        <v>0.05972632312047128</v>
+        <v>0.09433013798463455</v>
       </c>
       <c r="AC7">
-        <v>-0.03107564707109882</v>
+        <v>-0.07447347610560454</v>
       </c>
       <c r="AD7">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>2.9</v>
+        <v>3.4</v>
       </c>
       <c r="AG7">
-        <v>-1.93</v>
+        <v>-17.4</v>
       </c>
       <c r="AH7">
-        <v>0.01481103166496425</v>
+        <v>0.01190476190476191</v>
       </c>
       <c r="AI7">
-        <v>0.005682931608857535</v>
+        <v>0.006965785699651711</v>
       </c>
       <c r="AJ7">
-        <v>-0.01010629941875687</v>
+        <v>-0.06570996978851965</v>
       </c>
       <c r="AK7">
-        <v>-0.003818228579341999</v>
+        <v>-0.03723518082602183</v>
       </c>
       <c r="AL7">
-        <v>0.068</v>
+        <v>0.127</v>
       </c>
       <c r="AM7">
-        <v>0.068</v>
+        <v>0.127</v>
       </c>
       <c r="AN7">
-        <v>0.1870967741935484</v>
+        <v>0.3177570093457944</v>
       </c>
       <c r="AO7">
-        <v>177.9411764705882</v>
+        <v>77.8740157480315</v>
       </c>
       <c r="AP7">
-        <v>-0.1245161290322581</v>
+        <v>-1.626168224299066</v>
       </c>
       <c r="AQ7">
-        <v>177.9411764705882</v>
+        <v>77.8740157480315</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/romania/romania_investments_asset_management.xlsx
+++ b/research/traditional_assets/database/data/romania/romania_investments_asset_management.xlsx
@@ -588,121 +588,121 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.138</v>
+        <v>-0.039445</v>
       </c>
       <c r="E2">
-        <v>0.19</v>
+        <v>0.04725000000000001</v>
       </c>
       <c r="G2">
-        <v>0.1064595993697952</v>
+        <v>0.5295918367346939</v>
       </c>
       <c r="H2">
-        <v>0.1064595993697952</v>
+        <v>0.5295918367346939</v>
       </c>
       <c r="I2">
-        <v>0.8977342636356814</v>
+        <v>-1.228061224489796</v>
       </c>
       <c r="J2">
-        <v>0.8603639133853898</v>
+        <v>-1.137779348634375</v>
       </c>
       <c r="K2">
-        <v>1166.8</v>
+        <v>-233.2</v>
       </c>
       <c r="L2">
-        <v>0.8753844999624877</v>
+        <v>-1.189795918367347</v>
       </c>
       <c r="M2">
-        <v>313.473</v>
+        <v>1653.285</v>
       </c>
       <c r="N2">
-        <v>0.08917389696469719</v>
+        <v>1.099404841069291</v>
       </c>
       <c r="O2">
-        <v>0.2686604388069935</v>
+        <v>-7.08955831903945</v>
       </c>
       <c r="P2">
-        <v>78.706</v>
+        <v>1446.365</v>
       </c>
       <c r="Q2">
-        <v>0.022389554234347</v>
+        <v>0.9618067562175822</v>
       </c>
       <c r="R2">
-        <v>0.06745457661981488</v>
+        <v>-6.202251286449399</v>
       </c>
       <c r="S2">
-        <v>234.767</v>
+        <v>206.92</v>
       </c>
       <c r="T2">
-        <v>0.7489225547335814</v>
+        <v>0.1251568846266675</v>
       </c>
       <c r="U2">
-        <v>125.17</v>
+        <v>375.654</v>
       </c>
       <c r="V2">
-        <v>0.0356072027991921</v>
+        <v>0.2498031653145365</v>
       </c>
       <c r="W2">
-        <v>0.06008178672538535</v>
+        <v>0.02966485507246376</v>
       </c>
       <c r="X2">
-        <v>0.09434184640869402</v>
+        <v>0.07874610478815983</v>
       </c>
       <c r="Y2">
-        <v>-0.03426005968330867</v>
+        <v>-0.04908124971569607</v>
       </c>
       <c r="Z2">
-        <v>0.2810967941805857</v>
+        <v>0.04138074017898859</v>
       </c>
       <c r="AA2">
-        <v>0.05629511888204518</v>
+        <v>0.02764661344693578</v>
       </c>
       <c r="AB2">
-        <v>0.09413513067646434</v>
+        <v>0.07873957220819873</v>
       </c>
       <c r="AC2">
-        <v>-0.03784001179441916</v>
+        <v>-0.05109295876126295</v>
       </c>
       <c r="AD2">
-        <v>10.371</v>
+        <v>28.416</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>10.371</v>
+        <v>28.416</v>
       </c>
       <c r="AG2">
-        <v>-114.799</v>
+        <v>-347.238</v>
       </c>
       <c r="AH2">
-        <v>0.002941567718598814</v>
+        <v>0.01854568807531053</v>
       </c>
       <c r="AI2">
-        <v>0.002113868432225456</v>
+        <v>0.009688651158096584</v>
       </c>
       <c r="AJ2">
-        <v>-0.03375943721234018</v>
+        <v>-0.3002329317407973</v>
       </c>
       <c r="AK2">
-        <v>-0.02401149884720794</v>
+        <v>-0.1357850701257829</v>
       </c>
       <c r="AL2">
-        <v>0.397</v>
+        <v>1.496</v>
       </c>
       <c r="AM2">
-        <v>0.397</v>
+        <v>1.496</v>
       </c>
       <c r="AN2">
-        <v>0.109630021141649</v>
+        <v>0.208481291269259</v>
       </c>
       <c r="AO2">
-        <v>3014.080604534005</v>
+        <v>-160.8957219251337</v>
       </c>
       <c r="AP2">
-        <v>-1.213520084566596</v>
+        <v>-2.547600880410858</v>
       </c>
       <c r="AQ2">
-        <v>3014.080604534005</v>
+        <v>-160.8957219251337</v>
       </c>
     </row>
     <row r="3">
@@ -713,7 +713,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Fondul Proprietatea SA (BVB:FP)</t>
+          <t>Transilvania Investments Alliance S.A. (BVB:TRANSI)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -722,115 +722,121 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.418</v>
+        <v>0.162</v>
       </c>
       <c r="E3">
-        <v>0.473</v>
+        <v>0.181</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>0.3194805194805195</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.3194805194805195</v>
       </c>
       <c r="I3">
-        <v>0.9787704555506413</v>
+        <v>0.8389610389610389</v>
       </c>
       <c r="J3">
-        <v>0.9775691752146796</v>
+        <v>0.8364172503880958</v>
       </c>
       <c r="K3">
-        <v>1074.2</v>
+        <v>34.2</v>
       </c>
       <c r="L3">
-        <v>0.9501990269792128</v>
+        <v>0.8883116883116884</v>
       </c>
       <c r="M3">
-        <v>278.7</v>
+        <v>5.19</v>
       </c>
       <c r="N3">
-        <v>0.1046957175056349</v>
+        <v>0.03322663252240717</v>
       </c>
       <c r="O3">
-        <v>0.2594488921988456</v>
+        <v>0.1517543859649123</v>
       </c>
       <c r="P3">
-        <v>59.3</v>
+        <v>4.12</v>
       </c>
       <c r="Q3">
-        <v>0.02227648384673178</v>
+        <v>0.02637644046094751</v>
       </c>
       <c r="R3">
-        <v>0.05520387264941351</v>
+        <v>0.1204678362573099</v>
       </c>
       <c r="S3">
-        <v>219.4</v>
+        <v>1.07</v>
       </c>
       <c r="T3">
-        <v>0.7872264083243631</v>
+        <v>0.2061657032755299</v>
       </c>
       <c r="U3">
-        <v>55.3</v>
+        <v>15.4</v>
       </c>
       <c r="V3">
-        <v>0.02077385424492862</v>
+        <v>0.09859154929577466</v>
       </c>
       <c r="W3">
-        <v>0.3740641431904447</v>
+        <v>0.1348580441640379</v>
       </c>
       <c r="X3">
-        <v>0.09404034272219189</v>
+        <v>0.07888224685189935</v>
       </c>
       <c r="Y3">
-        <v>0.2800238004682528</v>
+        <v>0.05597579731213853</v>
       </c>
       <c r="Z3">
-        <v>0.4085209409894121</v>
+        <v>0.1552776242926802</v>
       </c>
       <c r="AA3">
-        <v>0.3993574793409444</v>
+        <v>0.1298768835576793</v>
       </c>
       <c r="AB3">
-        <v>0.09404034272219189</v>
+        <v>0.07879111428854782</v>
       </c>
       <c r="AC3">
-        <v>0.3053171366187525</v>
+        <v>0.05108576926913153</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.6830000000000001</v>
       </c>
       <c r="AG3">
-        <v>-55.3</v>
+        <v>-14.717</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.004353562846197485</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.002021409777940885</v>
       </c>
       <c r="AJ3">
-        <v>-0.02121456247362566</v>
+        <v>-0.1040195641879237</v>
       </c>
       <c r="AK3">
-        <v>-0.01843026162306282</v>
+        <v>-0.04563651417284012</v>
       </c>
       <c r="AL3">
-        <v>0.012</v>
+        <v>0.02</v>
       </c>
       <c r="AM3">
-        <v>0.012</v>
+        <v>0.02</v>
+      </c>
+      <c r="AN3">
+        <v>0.02101538461538462</v>
       </c>
       <c r="AO3">
-        <v>92208.33333333333</v>
+        <v>1615</v>
+      </c>
+      <c r="AP3">
+        <v>-0.4528307692307693</v>
       </c>
       <c r="AQ3">
-        <v>92208.33333333333</v>
+        <v>1615</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>S.I.F. Oltenia S.A. (BVB:SIF5)</t>
+          <t>Lion Capital S.A. (BVB:LION)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -849,110 +855,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.00229</v>
+      </c>
+      <c r="E4">
+        <v>0.251</v>
+      </c>
       <c r="G4">
-        <v>0.0974188176519567</v>
+        <v>0.2775061124694376</v>
       </c>
       <c r="H4">
-        <v>0.0974188176519567</v>
+        <v>0.2775061124694376</v>
       </c>
       <c r="I4">
-        <v>0.3430474604496254</v>
+        <v>0.8924205378973106</v>
       </c>
       <c r="J4">
-        <v>0.3179013585478144</v>
+        <v>0.8529199567116919</v>
       </c>
       <c r="K4">
-        <v>38.6</v>
+        <v>70</v>
       </c>
       <c r="L4">
-        <v>0.3213988343047461</v>
+        <v>0.8557457212713937</v>
       </c>
       <c r="M4">
-        <v>5.781999999999999</v>
+        <v>1.061</v>
       </c>
       <c r="N4">
-        <v>0.03275920679886685</v>
+        <v>0.003639794168096055</v>
       </c>
       <c r="O4">
-        <v>0.1497927461139896</v>
+        <v>0.01515714285714286</v>
       </c>
       <c r="P4">
-        <v>5.77</v>
+        <v>0.041</v>
       </c>
       <c r="Q4">
-        <v>0.03269121813031161</v>
+        <v>0.0001406518010291595</v>
       </c>
       <c r="R4">
-        <v>0.1494818652849741</v>
+        <v>0.0005857142857142858</v>
       </c>
       <c r="S4">
-        <v>0.01199999999999957</v>
+        <v>1.02</v>
       </c>
       <c r="T4">
-        <v>0.00207540643375987</v>
+        <v>0.9613572101790764</v>
       </c>
       <c r="U4">
-        <v>2.78</v>
+        <v>60</v>
       </c>
       <c r="V4">
-        <v>0.01575070821529745</v>
+        <v>0.2058319039451115</v>
       </c>
       <c r="W4">
-        <v>0.07746337547662051</v>
+        <v>0.1180040458530007</v>
       </c>
       <c r="X4">
-        <v>0.09562300201441615</v>
+        <v>0.07874361980232025</v>
       </c>
       <c r="Y4">
-        <v>-0.01815962653779564</v>
+        <v>0.03926042605068042</v>
       </c>
       <c r="Z4">
-        <v>0.247695258522903</v>
+        <v>0.1477820052825743</v>
       </c>
       <c r="AA4">
-        <v>0.07874265919028298</v>
+        <v>0.1260462215483803</v>
       </c>
       <c r="AB4">
-        <v>0.09452462098381804</v>
+        <v>0.0787386275295265</v>
       </c>
       <c r="AC4">
-        <v>-0.01578196179353507</v>
+        <v>0.0473075940188538</v>
       </c>
       <c r="AD4">
-        <v>6.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>6.02</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG4">
-        <v>3.24</v>
+        <v>-59.93</v>
       </c>
       <c r="AH4">
-        <v>0.03298268682884067</v>
+        <v>0.0002400795692286587</v>
       </c>
       <c r="AI4">
-        <v>0.01170022545284926</v>
+        <v>8.68518679355311e-05</v>
       </c>
       <c r="AJ4">
-        <v>0.01802603760988094</v>
+        <v>-0.2587986354018224</v>
       </c>
       <c r="AK4">
-        <v>0.006331340133661625</v>
+        <v>-0.08033835140823357</v>
       </c>
       <c r="AL4">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AM4">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN4">
-        <v>0.1346756152125279</v>
+        <v>0.0009562841530054646</v>
+      </c>
+      <c r="AO4">
+        <v>811.1111111111111</v>
       </c>
       <c r="AP4">
-        <v>0.07248322147651005</v>
+        <v>-0.8187158469945355</v>
+      </c>
+      <c r="AQ4">
+        <v>811.1111111111111</v>
       </c>
     </row>
     <row r="5">
@@ -963,7 +981,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Transilvania Investments Alliance S.A. (BVB:TRANSI)</t>
+          <t>Infinity Capital Investments S.A. (BVB:INFINITY)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -972,121 +990,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.138</v>
+        <v>-0.108</v>
       </c>
       <c r="E5">
-        <v>0.19</v>
+        <v>-0.08650000000000001</v>
       </c>
       <c r="G5">
-        <v>0.9454545454545454</v>
+        <v>1.258793969849246</v>
       </c>
       <c r="H5">
-        <v>0.9454545454545454</v>
+        <v>1.258793969849246</v>
       </c>
       <c r="I5">
-        <v>0.7727272727272727</v>
+        <v>0.4020100502512563</v>
       </c>
       <c r="J5">
-        <v>0.7727272727272727</v>
+        <v>0.3275637446491718</v>
       </c>
       <c r="K5">
-        <v>19.1</v>
+        <v>13.1</v>
       </c>
       <c r="L5">
-        <v>0.8681818181818183</v>
+        <v>0.3291457286432161</v>
       </c>
       <c r="M5">
-        <v>1.111</v>
+        <v>7.234</v>
       </c>
       <c r="N5">
-        <v>0.008666146645865836</v>
+        <v>0.03607980049875312</v>
       </c>
       <c r="O5">
-        <v>0.0581675392670157</v>
+        <v>0.5522137404580153</v>
       </c>
       <c r="P5">
-        <v>0.216</v>
+        <v>0.504</v>
       </c>
       <c r="Q5">
-        <v>0.001684867394695788</v>
+        <v>0.002513715710723192</v>
       </c>
       <c r="R5">
-        <v>0.01130890052356021</v>
+        <v>0.03847328244274809</v>
       </c>
       <c r="S5">
-        <v>0.895</v>
+        <v>6.73</v>
       </c>
       <c r="T5">
-        <v>0.8055805580558056</v>
+        <v>0.9303290019353055</v>
       </c>
       <c r="U5">
-        <v>6.49</v>
+        <v>0.254</v>
       </c>
       <c r="V5">
-        <v>0.05062402496099844</v>
+        <v>0.001266832917705736</v>
       </c>
       <c r="W5">
-        <v>0.06008178672538535</v>
+        <v>0.02966485507246376</v>
       </c>
       <c r="X5">
-        <v>0.09434184640869402</v>
+        <v>0.07874610478815983</v>
       </c>
       <c r="Y5">
-        <v>-0.03426005968330867</v>
+        <v>-0.04908124971569607</v>
       </c>
       <c r="Z5">
-        <v>0.07285250678852905</v>
+        <v>0.08440071252862837</v>
       </c>
       <c r="AA5">
-        <v>0.05629511888204518</v>
+        <v>0.02764661344693578</v>
       </c>
       <c r="AB5">
-        <v>0.09413513067646434</v>
+        <v>0.07873957220819873</v>
       </c>
       <c r="AC5">
-        <v>-0.03784001179441916</v>
+        <v>-0.05109295876126295</v>
       </c>
       <c r="AD5">
-        <v>0.833</v>
+        <v>0.063</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>0.833</v>
+        <v>0.063</v>
       </c>
       <c r="AG5">
-        <v>-5.657</v>
+        <v>-0.191</v>
       </c>
       <c r="AH5">
-        <v>0.006455712879650942</v>
+        <v>0.000314115764123991</v>
       </c>
       <c r="AI5">
-        <v>0.003273946382741233</v>
+        <v>0.0001149712663081267</v>
       </c>
       <c r="AJ5">
-        <v>-0.04616338754559624</v>
+        <v>-0.0009535268010923124</v>
       </c>
       <c r="AK5">
-        <v>-0.02281572780840758</v>
+        <v>-0.0003487253267702375</v>
       </c>
       <c r="AL5">
-        <v>0.171</v>
+        <v>0.725</v>
       </c>
       <c r="AM5">
-        <v>0.171</v>
+        <v>0.725</v>
       </c>
       <c r="AN5">
-        <v>0.04871345029239765</v>
+        <v>0.00375</v>
       </c>
       <c r="AO5">
-        <v>99.41520467836257</v>
+        <v>22.06896551724138</v>
       </c>
       <c r="AP5">
-        <v>-0.3308187134502923</v>
+        <v>-0.01136904761904762</v>
       </c>
       <c r="AQ5">
-        <v>99.41520467836257</v>
+        <v>22.06896551724138</v>
       </c>
     </row>
     <row r="6">
@@ -1097,7 +1115,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SIF Banat-Crisana (BVB:SIF1)</t>
+          <t>Evergent Investments SA (BVB:EVER)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1105,116 +1123,122 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
+      <c r="D6">
+        <v>-0.0766</v>
+      </c>
+      <c r="E6">
+        <v>-0.168</v>
+      </c>
       <c r="G6">
-        <v>3.301003344481606</v>
+        <v>0.520891364902507</v>
       </c>
       <c r="H6">
-        <v>3.301003344481606</v>
+        <v>0.520891364902507</v>
       </c>
       <c r="I6">
-        <v>0.7357859531772576</v>
+        <v>0.3565459610027856</v>
       </c>
       <c r="J6">
-        <v>0.6695652173913045</v>
+        <v>0.3083768377944622</v>
       </c>
       <c r="K6">
-        <v>20</v>
+        <v>13.1</v>
       </c>
       <c r="L6">
-        <v>0.6688963210702341</v>
+        <v>0.3649025069637883</v>
       </c>
       <c r="M6">
-        <v>8.559999999999999</v>
+        <v>26</v>
       </c>
       <c r="N6">
-        <v>0.03213213213213213</v>
+        <v>0.1003086419753086</v>
       </c>
       <c r="O6">
-        <v>0.4279999999999999</v>
+        <v>1.984732824427481</v>
       </c>
       <c r="P6">
-        <v>3.79</v>
+        <v>13.1</v>
       </c>
       <c r="Q6">
-        <v>0.01422672672672673</v>
+        <v>0.05054012345679013</v>
       </c>
       <c r="R6">
-        <v>0.1895</v>
+        <v>1</v>
       </c>
       <c r="S6">
-        <v>4.769999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="T6">
-        <v>0.5572429906542056</v>
+        <v>0.4961538461538462</v>
       </c>
       <c r="U6">
-        <v>39.8</v>
+        <v>13.6</v>
       </c>
       <c r="V6">
-        <v>0.1493993993993994</v>
+        <v>0.05246913580246914</v>
       </c>
       <c r="W6">
-        <v>0.02540650406504065</v>
+        <v>0.02721795138167463</v>
       </c>
       <c r="X6">
-        <v>0.09406089611097052</v>
+        <v>0.08230757854186614</v>
       </c>
       <c r="Y6">
-        <v>-0.06865439204592987</v>
+        <v>-0.05508962716019151</v>
       </c>
       <c r="Z6">
-        <v>0.04203671393805278</v>
+        <v>0.07754081152183022</v>
       </c>
       <c r="AA6">
-        <v>0.02814632150634839</v>
+        <v>0.02391179025711841</v>
       </c>
       <c r="AB6">
-        <v>0.09404684348627286</v>
+        <v>0.07996348385713135</v>
       </c>
       <c r="AC6">
-        <v>-0.06590052197992448</v>
+        <v>-0.05605169360001295</v>
       </c>
       <c r="AD6">
-        <v>0.118</v>
+        <v>27.6</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>0.118</v>
+        <v>27.6</v>
       </c>
       <c r="AG6">
-        <v>-39.682</v>
+        <v>14</v>
       </c>
       <c r="AH6">
-        <v>0.0004427468313584824</v>
+        <v>0.09623430962343096</v>
       </c>
       <c r="AI6">
-        <v>0.0001988815441297921</v>
+        <v>0.05268180950563085</v>
       </c>
       <c r="AJ6">
-        <v>-0.1750280083628119</v>
+        <v>0.05124450951683749</v>
       </c>
       <c r="AK6">
-        <v>-0.0716905321958816</v>
+        <v>0.02743484224965707</v>
       </c>
       <c r="AL6">
-        <v>0.08699999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="AM6">
-        <v>0.08699999999999999</v>
+        <v>0.647</v>
       </c>
       <c r="AN6">
-        <v>0.005339366515837104</v>
+        <v>2</v>
       </c>
       <c r="AO6">
-        <v>252.8735632183908</v>
+        <v>19.78361669242658</v>
       </c>
       <c r="AP6">
-        <v>-1.795565610859728</v>
+        <v>1.014492753623188</v>
       </c>
       <c r="AQ6">
-        <v>252.8735632183908</v>
+        <v>19.78361669242658</v>
       </c>
     </row>
     <row r="7">
@@ -1225,7 +1249,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Evergent Investments S.A. (BVB:EVER)</t>
+          <t>Fondul Proprietatea SA (BVB:FP)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1233,122 +1257,95 @@
           <t>Investments &amp; Asset Management</t>
         </is>
       </c>
-      <c r="D7">
-        <v>-0.07290000000000001</v>
-      </c>
-      <c r="E7">
-        <v>-0.0499</v>
-      </c>
-      <c r="G7">
-        <v>0.3519736842105263</v>
-      </c>
-      <c r="H7">
-        <v>0.3519736842105263</v>
-      </c>
-      <c r="I7">
-        <v>0.3253289473684211</v>
-      </c>
-      <c r="J7">
-        <v>0.3111421344103931</v>
-      </c>
       <c r="K7">
-        <v>14.9</v>
-      </c>
-      <c r="L7">
-        <v>0.4901315789473685</v>
+        <v>-363.6</v>
       </c>
       <c r="M7">
-        <v>19.32</v>
+        <v>1613.8</v>
       </c>
       <c r="N7">
-        <v>0.06846208362863218</v>
+        <v>2.705902079141516</v>
       </c>
       <c r="O7">
-        <v>1.296644295302013</v>
+        <v>-4.438393839383938</v>
       </c>
       <c r="P7">
-        <v>9.630000000000001</v>
+        <v>1428.6</v>
       </c>
       <c r="Q7">
-        <v>0.03412473423104182</v>
+        <v>2.395372233400402</v>
       </c>
       <c r="R7">
-        <v>0.6463087248322148</v>
+        <v>-3.929042904290429</v>
       </c>
       <c r="S7">
-        <v>9.69</v>
+        <v>185.2</v>
       </c>
       <c r="T7">
-        <v>0.5015527950310559</v>
+        <v>0.1147601933325072</v>
       </c>
       <c r="U7">
-        <v>20.8</v>
+        <v>286.4</v>
       </c>
       <c r="V7">
-        <v>0.07370659107016302</v>
+        <v>0.4802146210596915</v>
       </c>
       <c r="W7">
-        <v>0.02795497185741088</v>
+        <v>-0.1189868446887885</v>
       </c>
       <c r="X7">
-        <v>0.09459940161239239</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="Y7">
-        <v>-0.0666444297549815</v>
+        <v>-0.1977224088781608</v>
       </c>
       <c r="Z7">
-        <v>0.06381862076204471</v>
+        <v>0</v>
       </c>
       <c r="AA7">
-        <v>0.01985666187903002</v>
+        <v>-0.1249125145809032</v>
       </c>
       <c r="AB7">
-        <v>0.09433013798463455</v>
+        <v>0.07873556418937229</v>
       </c>
       <c r="AC7">
-        <v>-0.07447347610560454</v>
+        <v>-0.2036480787702755</v>
       </c>
       <c r="AD7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AE7">
         <v>0</v>
       </c>
       <c r="AF7">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="AG7">
-        <v>-17.4</v>
+        <v>-286.4</v>
       </c>
       <c r="AH7">
-        <v>0.01190476190476191</v>
+        <v>0</v>
       </c>
       <c r="AI7">
-        <v>0.006965785699651711</v>
+        <v>0</v>
       </c>
       <c r="AJ7">
-        <v>-0.06570996978851965</v>
+        <v>-0.9238709677419354</v>
       </c>
       <c r="AK7">
-        <v>-0.03723518082602183</v>
+        <v>-0.6648096564531103</v>
       </c>
       <c r="AL7">
-        <v>0.127</v>
+        <v>0.014</v>
       </c>
       <c r="AM7">
-        <v>0.127</v>
-      </c>
-      <c r="AN7">
-        <v>0.3177570093457944</v>
+        <v>0.014</v>
       </c>
       <c r="AO7">
-        <v>77.8740157480315</v>
-      </c>
-      <c r="AP7">
-        <v>-1.626168224299066</v>
+        <v>-26771.42857142857</v>
       </c>
       <c r="AQ7">
-        <v>77.8740157480315</v>
+        <v>-26771.42857142857</v>
       </c>
     </row>
   </sheetData>
